--- a/site/Set-Up-Webhooks-in-UKG-Pro/headings.xlsx
+++ b/site/Set-Up-Webhooks-in-UKG-Pro/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,20 +529,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Obtaining Event URL and Token</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>h_01M3BWDTN18WZ645G9HNH5CR2T</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Set-Up-Webhooks-in-UKG-Pro/#h_01M3BWDTN18WZ645G9HNH5CR2T</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>References</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>h_01JRJE88PCS8VGBZB58Y4KE7F7</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Set-Up-Webhooks-in-UKG-Pro/#h_01JRJE88PCS8VGBZB58Y4KE7F7</t>
         </is>

--- a/site/Set-Up-Webhooks-in-UKG-Pro/headings.xlsx
+++ b/site/Set-Up-Webhooks-in-UKG-Pro/headings.xlsx
@@ -539,12 +539,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>h_01M3BWDTN18WZ645G9HNH5CR2T</t>
+          <t>h_01M3C03VJVKRXW874E80T1NYJ7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Set-Up-Webhooks-in-UKG-Pro/#h_01M3BWDTN18WZ645G9HNH5CR2T</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Set-Up-Webhooks-in-UKG-Pro/#h_01M3C03VJVKRXW874E80T1NYJ7</t>
         </is>
       </c>
     </row>
